--- a/backend/scripts/audit-output/expeditor-smoke/ex-5.1.2.xlsx
+++ b/backend/scripts/audit-output/expeditor-smoke/ex-5.1.2.xlsx
@@ -14,9 +14,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="123">
-  <si>
-    <t>Загрузочный лист 5.1.2 (Время печати: 27.05.2026 19:51:40)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+  <si>
+    <t>Загрузочный лист 5.1.2 (Время печати: 28.05.2026 17:37:19)</t>
   </si>
   <si>
     <t>b7_848</t>
@@ -879,7 +879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:AS52"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -1488,9 +1488,7 @@
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="14"/>
-      <c r="E8" s="14">
-        <v>45</v>
-      </c>
+      <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
       <c r="H8" s="14"/>
@@ -1543,12 +1541,8 @@
       <c r="D9" s="3">
         <v>25500</v>
       </c>
-      <c r="E9" s="3">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3">
-        <v>5</v>
-      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -1712,12 +1706,8 @@
       <c r="D12" s="3">
         <v>25500</v>
       </c>
-      <c r="E12" s="3">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3">
-        <v>3</v>
-      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -1822,9 +1812,7 @@
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="14"/>
-      <c r="E14" s="14">
-        <v>14</v>
-      </c>
+      <c r="E14" s="14"/>
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
       <c r="H14" s="14"/>
@@ -1983,9 +1971,7 @@
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="14"/>
-      <c r="E17" s="14">
-        <v>465</v>
-      </c>
+      <c r="E17" s="14"/>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
       <c r="H17" s="14"/>
@@ -2199,9 +2185,7 @@
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="14"/>
-      <c r="E21" s="14">
-        <v>183</v>
-      </c>
+      <c r="E21" s="14"/>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
@@ -2470,9 +2454,7 @@
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="14"/>
-      <c r="E26" s="14">
-        <v>32</v>
-      </c>
+      <c r="E26" s="14"/>
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
@@ -3049,45 +3031,123 @@
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="3"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
-      <c r="M37" s="18"/>
-      <c r="N37" s="18"/>
-      <c r="O37" s="18"/>
-      <c r="P37" s="18"/>
-      <c r="Q37" s="18"/>
-      <c r="R37" s="18"/>
-      <c r="S37" s="18"/>
-      <c r="T37" s="18"/>
-      <c r="U37" s="18"/>
-      <c r="V37" s="18"/>
-      <c r="W37" s="18"/>
-      <c r="X37" s="18"/>
-      <c r="Y37" s="18"/>
-      <c r="Z37" s="18"/>
-      <c r="AA37" s="18"/>
-      <c r="AB37" s="18"/>
-      <c r="AC37" s="18"/>
-      <c r="AD37" s="18"/>
-      <c r="AE37" s="18"/>
-      <c r="AF37" s="18"/>
-      <c r="AG37" s="18"/>
-      <c r="AH37" s="18"/>
-      <c r="AI37" s="18"/>
-      <c r="AJ37" s="18"/>
-      <c r="AK37" s="18"/>
-      <c r="AL37" s="18"/>
-      <c r="AM37" s="18"/>
-      <c r="AN37" s="18"/>
-      <c r="AO37" s="18"/>
-      <c r="AP37" s="18"/>
-      <c r="AQ37" s="18"/>
+      <c r="E37" s="18">
+        <v>939</v>
+      </c>
+      <c r="F37" s="18">
+        <v>16</v>
+      </c>
+      <c r="G37" s="18">
+        <v>6</v>
+      </c>
+      <c r="H37" s="18">
+        <v>20</v>
+      </c>
+      <c r="I37" s="18">
+        <v>40</v>
+      </c>
+      <c r="J37" s="18">
+        <v>3</v>
+      </c>
+      <c r="K37" s="18">
+        <v>8</v>
+      </c>
+      <c r="L37" s="18">
+        <v>24</v>
+      </c>
+      <c r="M37" s="18">
+        <v>20</v>
+      </c>
+      <c r="N37" s="18">
+        <v>0</v>
+      </c>
+      <c r="O37" s="18">
+        <v>12</v>
+      </c>
+      <c r="P37" s="18">
+        <v>180</v>
+      </c>
+      <c r="Q37" s="18">
+        <v>22</v>
+      </c>
+      <c r="R37" s="18">
+        <v>64</v>
+      </c>
+      <c r="S37" s="18">
+        <v>16</v>
+      </c>
+      <c r="T37" s="18">
+        <v>25</v>
+      </c>
+      <c r="U37" s="18">
+        <v>21</v>
+      </c>
+      <c r="V37" s="18">
+        <v>6</v>
+      </c>
+      <c r="W37" s="18">
+        <v>22</v>
+      </c>
+      <c r="X37" s="18">
+        <v>6</v>
+      </c>
+      <c r="Y37" s="18">
+        <v>20</v>
+      </c>
+      <c r="Z37" s="18">
+        <v>16</v>
+      </c>
+      <c r="AA37" s="18">
+        <v>20</v>
+      </c>
+      <c r="AB37" s="18">
+        <v>28</v>
+      </c>
+      <c r="AC37" s="18">
+        <v>20</v>
+      </c>
+      <c r="AD37" s="18">
+        <v>20</v>
+      </c>
+      <c r="AE37" s="18">
+        <v>12</v>
+      </c>
+      <c r="AF37" s="18">
+        <v>8</v>
+      </c>
+      <c r="AG37" s="18">
+        <v>24</v>
+      </c>
+      <c r="AH37" s="18">
+        <v>20</v>
+      </c>
+      <c r="AI37" s="18">
+        <v>80</v>
+      </c>
+      <c r="AJ37" s="18">
+        <v>16</v>
+      </c>
+      <c r="AK37" s="18">
+        <v>8</v>
+      </c>
+      <c r="AL37" s="18">
+        <v>20</v>
+      </c>
+      <c r="AM37" s="18">
+        <v>40</v>
+      </c>
+      <c r="AN37" s="18">
+        <v>20</v>
+      </c>
+      <c r="AO37" s="18">
+        <v>24</v>
+      </c>
+      <c r="AP37" s="18">
+        <v>0</v>
+      </c>
+      <c r="AQ37" s="18">
+        <v>32</v>
+      </c>
       <c r="AR37" s="18"/>
       <c r="AS37" s="18"/>
     </row>
@@ -3098,45 +3158,123 @@
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="3"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
-      <c r="L38" s="18"/>
-      <c r="M38" s="18"/>
-      <c r="N38" s="18"/>
-      <c r="O38" s="18"/>
-      <c r="P38" s="18"/>
-      <c r="Q38" s="18"/>
-      <c r="R38" s="18"/>
-      <c r="S38" s="18"/>
-      <c r="T38" s="18"/>
-      <c r="U38" s="18"/>
-      <c r="V38" s="18"/>
-      <c r="W38" s="18"/>
-      <c r="X38" s="18"/>
-      <c r="Y38" s="18"/>
-      <c r="Z38" s="18"/>
-      <c r="AA38" s="18"/>
-      <c r="AB38" s="18"/>
-      <c r="AC38" s="18"/>
-      <c r="AD38" s="18"/>
-      <c r="AE38" s="18"/>
-      <c r="AF38" s="18"/>
-      <c r="AG38" s="18"/>
-      <c r="AH38" s="18"/>
-      <c r="AI38" s="18"/>
-      <c r="AJ38" s="18"/>
-      <c r="AK38" s="18"/>
-      <c r="AL38" s="18"/>
-      <c r="AM38" s="18"/>
-      <c r="AN38" s="18"/>
-      <c r="AO38" s="18"/>
-      <c r="AP38" s="18"/>
-      <c r="AQ38" s="18"/>
+      <c r="E38" s="18">
+        <v>37</v>
+      </c>
+      <c r="F38" s="18">
+        <v>0</v>
+      </c>
+      <c r="G38" s="18">
+        <v>0</v>
+      </c>
+      <c r="H38" s="18">
+        <v>0</v>
+      </c>
+      <c r="I38" s="18">
+        <v>0</v>
+      </c>
+      <c r="J38" s="18">
+        <v>0</v>
+      </c>
+      <c r="K38" s="18">
+        <v>0</v>
+      </c>
+      <c r="L38" s="18">
+        <v>0</v>
+      </c>
+      <c r="M38" s="18">
+        <v>0</v>
+      </c>
+      <c r="N38" s="18">
+        <v>0</v>
+      </c>
+      <c r="O38" s="18">
+        <v>0</v>
+      </c>
+      <c r="P38" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="18">
+        <v>0</v>
+      </c>
+      <c r="R38" s="18">
+        <v>0</v>
+      </c>
+      <c r="S38" s="18">
+        <v>0</v>
+      </c>
+      <c r="T38" s="18">
+        <v>0</v>
+      </c>
+      <c r="U38" s="18">
+        <v>0</v>
+      </c>
+      <c r="V38" s="18">
+        <v>0</v>
+      </c>
+      <c r="W38" s="18">
+        <v>0</v>
+      </c>
+      <c r="X38" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AI38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AL38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AM38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AN38" s="18">
+        <v>5</v>
+      </c>
+      <c r="AO38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AP38" s="18">
+        <v>0</v>
+      </c>
+      <c r="AQ38" s="18">
+        <v>32</v>
+      </c>
       <c r="AR38" s="18"/>
       <c r="AS38" s="18"/>
     </row>
@@ -3149,45 +3287,119 @@
       <c r="D39" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="E39" s="23"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="22"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="22"/>
+      <c r="E39" s="23">
+        <v>11676900</v>
+      </c>
+      <c r="F39" s="22">
+        <v>154800</v>
+      </c>
+      <c r="G39" s="22">
+        <v>153000</v>
+      </c>
+      <c r="H39" s="22">
+        <v>193500</v>
+      </c>
+      <c r="I39" s="22">
+        <v>387000</v>
+      </c>
+      <c r="J39" s="22">
+        <v>76500</v>
+      </c>
+      <c r="K39" s="22">
+        <v>294000</v>
+      </c>
+      <c r="L39" s="22">
+        <v>384400</v>
+      </c>
+      <c r="M39" s="22">
+        <v>207000</v>
+      </c>
       <c r="N39" s="22"/>
-      <c r="O39" s="22"/>
-      <c r="P39" s="22"/>
-      <c r="Q39" s="22"/>
-      <c r="R39" s="22"/>
-      <c r="S39" s="22"/>
-      <c r="T39" s="22"/>
-      <c r="U39" s="22"/>
-      <c r="V39" s="22"/>
-      <c r="W39" s="22"/>
-      <c r="X39" s="22"/>
-      <c r="Y39" s="22"/>
-      <c r="Z39" s="22"/>
-      <c r="AA39" s="22"/>
-      <c r="AB39" s="22"/>
-      <c r="AC39" s="22"/>
-      <c r="AD39" s="22"/>
-      <c r="AE39" s="22"/>
-      <c r="AF39" s="22"/>
-      <c r="AG39" s="22"/>
-      <c r="AH39" s="22"/>
-      <c r="AI39" s="22"/>
-      <c r="AJ39" s="22"/>
-      <c r="AK39" s="22"/>
-      <c r="AL39" s="22"/>
-      <c r="AM39" s="22"/>
-      <c r="AN39" s="22"/>
-      <c r="AO39" s="22"/>
+      <c r="O39" s="22">
+        <v>116100</v>
+      </c>
+      <c r="P39" s="22">
+        <v>2318000</v>
+      </c>
+      <c r="Q39" s="22">
+        <v>203800</v>
+      </c>
+      <c r="R39" s="22">
+        <v>619200</v>
+      </c>
+      <c r="S39" s="22">
+        <v>154800</v>
+      </c>
+      <c r="T39" s="22">
+        <v>577500</v>
+      </c>
+      <c r="U39" s="22">
+        <v>538800</v>
+      </c>
+      <c r="V39" s="22">
+        <v>153000</v>
+      </c>
+      <c r="W39" s="22">
+        <v>209200</v>
+      </c>
+      <c r="X39" s="22">
+        <v>115500</v>
+      </c>
+      <c r="Y39" s="22">
+        <v>193500</v>
+      </c>
+      <c r="Z39" s="22">
+        <v>154800</v>
+      </c>
+      <c r="AA39" s="22">
+        <v>193500</v>
+      </c>
+      <c r="AB39" s="22">
+        <v>270900</v>
+      </c>
+      <c r="AC39" s="22">
+        <v>714000</v>
+      </c>
+      <c r="AD39" s="22">
+        <v>207000</v>
+      </c>
+      <c r="AE39" s="22">
+        <v>116100</v>
+      </c>
+      <c r="AF39" s="22">
+        <v>77400</v>
+      </c>
+      <c r="AG39" s="22">
+        <v>240300</v>
+      </c>
+      <c r="AH39" s="22">
+        <v>193500</v>
+      </c>
+      <c r="AI39" s="22">
+        <v>774000</v>
+      </c>
+      <c r="AJ39" s="22">
+        <v>165600</v>
+      </c>
+      <c r="AK39" s="22">
+        <v>77400</v>
+      </c>
+      <c r="AL39" s="22">
+        <v>193500</v>
+      </c>
+      <c r="AM39" s="22">
+        <v>387000</v>
+      </c>
+      <c r="AN39" s="22">
+        <v>510000</v>
+      </c>
+      <c r="AO39" s="22">
+        <v>240300</v>
+      </c>
       <c r="AP39" s="22"/>
-      <c r="AQ39" s="22"/>
+      <c r="AQ39" s="22">
+        <v>112000</v>
+      </c>
       <c r="AR39" s="19"/>
       <c r="AS39" s="19"/>
     </row>
@@ -3979,6 +4191,6 @@
     <mergeCell ref="B52:C52"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.2" bottom="0.2" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>